--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationdispense.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationdispense.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2020" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1724" uniqueCount="370">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>ELGA e-Medikation MedicationDispense</t>
+    <t>ELGA e-Medikation Abgabe</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-13T12:36:36+00:00</t>
+    <t>2026-01-15T19:11:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>TODO</t>
+    <t>Abgabe</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.eu/fhir/mpd/StructureDefinition/MedicationDispense-eu-mpd</t>
+    <t>http://hl7.org/fhir/StructureDefinition/MedicationDispense</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -364,7 +364,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -425,21 +425,21 @@
     <t>MedicationDispense.extension</t>
   </si>
   <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>open</t>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
@@ -449,31 +449,7 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>MedicationDispense.extension:renderedDosageInstruction</t>
-  </si>
-  <si>
-    <t>renderedDosageInstruction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationDispense.renderedDosageInstruction}
-</t>
-  </si>
-  <si>
-    <t>Full representation of the dosage instructions</t>
-  </si>
-  <si>
-    <t>Optional Extension Element - found in all resources.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>MedicationDispense.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
   </si>
   <si>
     <t>Extensions that cannot be ignored</t>
@@ -483,9 +459,6 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -523,7 +496,7 @@
     <t>MedicationDispense.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Procedure)
+    <t xml:space="preserve">Reference(Procedure|4.0.1)
 </t>
   </si>
   <si>
@@ -576,7 +549,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(DetectedIssue)</t>
+Reference(DetectedIssue|4.0.1)</t>
   </si>
   <si>
     <t>Why a dispense was not performed</t>
@@ -591,7 +564,7 @@
     <t>A code describing why a dispense was not performed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -619,7 +592,7 @@
     <t>A code describing where the dispensed medication is expected to be consumed or administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-category|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication dispense"].value</t>
@@ -629,7 +602,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Medication)</t>
+Reference(Medication|4.0.1)</t>
   </si>
   <si>
     <t>What medication was supplied</t>
@@ -644,51 +617,110 @@
     <t>A coded concept identifying which substance or product can be dispensed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
+    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=PRD].role</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>CombinedMedicationRequest.component1.AdministrationRequest.consumable</t>
+  </si>
+  <si>
+    <t>RXD-2-Dispense/Give Code</t>
+  </si>
+  <si>
+    <t>MedicationDispense.subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1)
 </t>
   </si>
   <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>Event.code</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=PRD].role</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>CombinedMedicationRequest.component1.AdministrationRequest.consumable</t>
-  </si>
-  <si>
-    <t>RXD-2-Dispense/Give Code</t>
-  </si>
-  <si>
-    <t>MedicationDispense.medication[x]:medicationReference</t>
-  </si>
-  <si>
-    <t>medicationReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://hl7.eu/fhir/mpd/StructureDefinition/Medication-eu-mpd)
+    <t>Who the dispense is for</t>
+  </si>
+  <si>
+    <t>A link to a resource representing the person or the group to whom the medication will be given.</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration-&gt;subject-&gt;Patient.</t>
+  </si>
+  <si>
+    <t>Event.subject</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=SBJ].role[classCode=PAT]</t>
+  </si>
+  <si>
+    <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>PID-3-Patient ID List</t>
+  </si>
+  <si>
+    <t>MedicationDispense.context</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
-    <t>MedicationDispense.medication[x]:medicationCodeableConcept</t>
-  </si>
-  <si>
-    <t>medicationCodeableConcept</t>
-  </si>
-  <si>
-    <t>MedicationDispense.medication[x]:medicationCodeableConcept.id</t>
-  </si>
-  <si>
-    <t>MedicationDispense.medication[x].id</t>
+    <t>Encounter / Episode associated with event</t>
+  </si>
+  <si>
+    <t>The encounter or episode of care that establishes the context for this event.</t>
+  </si>
+  <si>
+    <t>Event.context</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=COMP].source[classCode=ENC, moodCode=EVN, code="type of encounter or episode"]</t>
+  </si>
+  <si>
+    <t>MedicationDispense.supportingInformation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Resource|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Information that supports the dispensing of the medication</t>
+  </si>
+  <si>
+    <t>Additional information that supports the medication being dispensed.</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=PERT].target[A_SupportingClinicalStatement CMET minimal with many different choices of classCodes(ORG, ENC, PROC, SPLY, SBADM, OBS) and each of the act class codes draws from one or more of the following moodCodes (EVN, DEF, INT PRMS, RQO, PRP, APT, ARQ, GOL)]</t>
+  </si>
+  <si>
+    <t>FiveWs.context</t>
+  </si>
+  <si>
+    <t>MedicationDispense.performer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Who performed event</t>
+  </si>
+  <si>
+    <t>Indicates who or what performed the event.</t>
+  </si>
+  <si>
+    <t>Event.performer</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=PRF]</t>
+  </si>
+  <si>
+    <t>MedicationDispense.performer.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -707,187 +739,13 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>MedicationDispense.medication[x]:medicationCodeableConcept.extension</t>
-  </si>
-  <si>
-    <t>MedicationDispense.medication[x].extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
+    <t>MedicationDispense.performer.extension</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
     <t>Element.extension</t>
-  </si>
-  <si>
-    <t>MedicationDispense.medication[x]:medicationCodeableConcept.extension:medication-absent-reason</t>
-  </si>
-  <si>
-    <t>medication-absent-reason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {data-absent-reason}
-</t>
-  </si>
-  <si>
-    <t>Reason for not providing the medication.</t>
-  </si>
-  <si>
-    <t>ANY.nullFlavor</t>
-  </si>
-  <si>
-    <t>MedicationDispense.medication[x]:medicationCodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>MedicationDispense.medication[x].coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>MedicationDispense.medication[x]:medicationCodeableConcept.text</t>
-  </si>
-  <si>
-    <t>MedicationDispense.medication[x].text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>MedicationDispense.subject</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Patient|Group)
-</t>
-  </si>
-  <si>
-    <t>Who the dispense is for</t>
-  </si>
-  <si>
-    <t>A link to a resource representing the person or the group to whom the medication will be given.</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration-&gt;subject-&gt;Patient.</t>
-  </si>
-  <si>
-    <t>Event.subject</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=SBJ].role[classCode=PAT]</t>
-  </si>
-  <si>
-    <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>PID-3-Patient ID List</t>
-  </si>
-  <si>
-    <t>MedicationDispense.context</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
-</t>
-  </si>
-  <si>
-    <t>Encounter / Episode associated with event</t>
-  </si>
-  <si>
-    <t>The encounter or episode of care that establishes the context for this event.</t>
-  </si>
-  <si>
-    <t>Event.context</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=COMP].source[classCode=ENC, moodCode=EVN, code="type of encounter or episode"]</t>
-  </si>
-  <si>
-    <t>MedicationDispense.supportingInformation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Resource)
-</t>
-  </si>
-  <si>
-    <t>Information that supports the dispensing of the medication</t>
-  </si>
-  <si>
-    <t>Additional information that supports the medication being dispensed.</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=PERT].target[A_SupportingClinicalStatement CMET minimal with many different choices of classCodes(ORG, ENC, PROC, SPLY, SBADM, OBS) and each of the act class codes draws from one or more of the following moodCodes (EVN, DEF, INT PRMS, RQO, PRP, APT, ARQ, GOL)]</t>
-  </si>
-  <si>
-    <t>FiveWs.context</t>
-  </si>
-  <si>
-    <t>MedicationDispense.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>Who performed event</t>
-  </si>
-  <si>
-    <t>Indicates who or what performed the event.</t>
-  </si>
-  <si>
-    <t>Event.performer</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=PRF]</t>
-  </si>
-  <si>
-    <t>MedicationDispense.performer.id</t>
-  </si>
-  <si>
-    <t>MedicationDispense.performer.extension</t>
   </si>
   <si>
     <t>MedicationDispense.performer.modifierExtension</t>
@@ -922,7 +780,7 @@
     <t>A code describing the role an individual played in dispensing a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function|4.0.1</t>
   </si>
   <si>
     <t>participation[typeCode=PRF].functionCode</t>
@@ -931,7 +789,7 @@
     <t>MedicationDispense.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Patient|Device|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|Patient|4.0.1|Device|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -950,7 +808,7 @@
     <t>MedicationDispense.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -966,7 +824,7 @@
     <t>MedicationDispense.authorizingPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.eu/fhir/mpd/StructureDefinition/MedicationRequest-eu-mpd)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1015,7 +873,7 @@
     <t>MedicationDispense.quantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1110,7 +968,7 @@
     <t>MedicationDispense.receiver</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1)
 </t>
   </si>
   <si>
@@ -1253,7 +1111,7 @@
     <t>MedicationDispense.substitution.responsibleParty</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1276,7 +1134,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue)
+    <t xml:space="preserve">Reference(DetectedIssue|4.0.1)
 </t>
   </si>
   <si>
@@ -1295,7 +1153,7 @@
     <t>MedicationDispense.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
@@ -1618,12 +1476,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO54"/>
+  <dimension ref="A1:AO46"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="80.65625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="41.2578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="41.2578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="23.5546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1631,7 +1489,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="89.75" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="93.98828125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1649,7 +1507,7 @@
     <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="40.16015625" customWidth="true" bestFit="true" hidden="true"/>
@@ -2612,7 +2470,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2631,15 +2489,17 @@
         <v>21</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>21</v>
@@ -2676,14 +2536,16 @@
         <v>21</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>137</v>
+        <v>21</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>138</v>
@@ -2704,7 +2566,7 @@
         <v>21</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>21</v>
@@ -2721,41 +2583,43 @@
         <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="M10" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>21</v>
       </c>
@@ -2803,7 +2667,7 @@
         <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -2812,7 +2676,7 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>139</v>
@@ -2835,14 +2699,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2855,26 +2719,24 @@
         <v>21</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="N11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>151</v>
-      </c>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>21</v>
       </c>
@@ -2922,7 +2784,7 @@
         <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -2934,19 +2796,19 @@
         <v>21</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>21</v>
+        <v>152</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>21</v>
@@ -2954,10 +2816,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2980,17 +2842,15 @@
         <v>21</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N12" t="s" s="2">
         <v>157</v>
       </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>21</v>
@@ -3039,7 +2899,7 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3060,10 +2920,10 @@
         <v>159</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>21</v>
@@ -3071,10 +2931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3082,30 +2942,32 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="L13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>21</v>
@@ -3130,13 +2992,13 @@
         <v>21</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>21</v>
+        <v>164</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>21</v>
+        <v>166</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>21</v>
@@ -3154,13 +3016,13 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>21</v>
@@ -3169,16 +3031,16 @@
         <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>21</v>
+        <v>169</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>21</v>
+        <v>170</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>21</v>
@@ -3186,10 +3048,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3197,7 +3059,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>88</v>
@@ -3206,23 +3068,21 @@
         <v>21</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>108</v>
+        <v>172</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>21</v>
@@ -3247,13 +3107,13 @@
         <v>21</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
@@ -3271,10 +3131,10 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>88</v>
@@ -3286,16 +3146,16 @@
         <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>177</v>
+        <v>21</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>178</v>
+        <v>21</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>21</v>
@@ -3303,10 +3163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3329,15 +3189,17 @@
         <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>21</v>
@@ -3362,13 +3224,13 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>183</v>
+        <v>112</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -3386,7 +3248,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3401,7 +3263,7 @@
         <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>186</v>
+        <v>21</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>187</v>
@@ -3429,7 +3291,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>88</v>
@@ -3441,7 +3303,7 @@
         <v>21</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>189</v>
@@ -3479,7 +3341,7 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>112</v>
+        <v>175</v>
       </c>
       <c r="Y16" t="s" s="2">
         <v>193</v>
@@ -3506,7 +3368,7 @@
         <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>88</v>
@@ -3518,27 +3380,27 @@
         <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>21</v>
+        <v>195</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>21</v>
+        <v>197</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>21</v>
+        <v>198</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>21</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3546,7 +3408,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>88</v>
@@ -3561,16 +3423,16 @@
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3596,32 +3458,34 @@
         <v>21</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>183</v>
+        <v>21</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AC17" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>88</v>
@@ -3642,22 +3506,20 @@
         <v>207</v>
       </c>
       <c r="AN17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>209</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>21</v>
       </c>
@@ -3675,20 +3537,18 @@
         <v>21</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="L18" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>200</v>
-      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3737,10 +3597,10 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>88</v>
@@ -3752,31 +3612,29 @@
         <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>207</v>
+        <v>21</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>208</v>
+        <v>21</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>21</v>
       </c>
@@ -3785,7 +3643,7 @@
         <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>21</v>
@@ -3794,20 +3652,18 @@
         <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -3832,13 +3688,13 @@
         <v>21</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>183</v>
+        <v>21</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>21</v>
@@ -3856,13 +3712,13 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>21</v>
@@ -3871,27 +3727,27 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>208</v>
+        <v>21</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3902,7 +3758,7 @@
         <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
@@ -3914,13 +3770,13 @@
         <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3971,25 +3827,25 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>21</v>
+        <v>225</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>21</v>
@@ -4003,21 +3859,21 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
@@ -4029,17 +3885,15 @@
         <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>133</v>
+        <v>228</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -4076,37 +3930,37 @@
         <v>21</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>226</v>
+        <v>21</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>137</v>
+        <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>21</v>
@@ -4120,23 +3974,21 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>21</v>
@@ -4148,15 +4000,17 @@
         <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>230</v>
+        <v>134</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>231</v>
+        <v>135</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -4205,7 +4059,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4237,14 +4091,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>21</v>
+        <v>237</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4257,25 +4111,25 @@
         <v>21</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>235</v>
+        <v>134</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>238</v>
+        <v>137</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>239</v>
+        <v>143</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -4336,13 +4190,13 @@
         <v>21</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>241</v>
+        <v>131</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>21</v>
@@ -4351,15 +4205,15 @@
         <v>21</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>242</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4379,22 +4233,20 @@
         <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>217</v>
+        <v>181</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>21</v>
@@ -4419,13 +4271,13 @@
         <v>21</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>21</v>
+        <v>245</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>21</v>
+        <v>246</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4443,7 +4295,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4461,7 +4313,7 @@
         <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>21</v>
@@ -4470,15 +4322,15 @@
         <v>21</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>251</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4486,7 +4338,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>88</v>
@@ -4498,20 +4350,18 @@
         <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>256</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>21</v>
@@ -4560,10 +4410,10 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>88</v>
@@ -4575,27 +4425,27 @@
         <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>259</v>
+        <v>21</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>260</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4618,13 +4468,13 @@
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4675,7 +4525,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4690,10 +4540,10 @@
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>265</v>
+        <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>21</v>
@@ -4707,10 +4557,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4733,15 +4583,17 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -4790,7 +4642,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4805,27 +4657,27 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>21</v>
+        <v>264</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>272</v>
+        <v>21</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>21</v>
+        <v>266</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>21</v>
+        <v>267</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4836,7 +4688,7 @@
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>21</v>
@@ -4848,13 +4700,13 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>274</v>
+        <v>181</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4881,13 +4733,13 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>21</v>
+        <v>270</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>21</v>
+        <v>271</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -4905,13 +4757,13 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>21</v>
@@ -4920,27 +4772,27 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>21</v>
+        <v>273</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>21</v>
+        <v>274</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4963,13 +4815,13 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>217</v>
+        <v>276</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>218</v>
+        <v>277</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>219</v>
+        <v>278</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5020,7 +4872,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>220</v>
+        <v>275</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5032,41 +4884,41 @@
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>221</v>
+        <v>279</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>21</v>
+        <v>280</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>21</v>
+        <v>281</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
@@ -5078,17 +4930,15 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>133</v>
+        <v>276</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -5137,25 +4987,25 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>227</v>
+        <v>282</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>221</v>
+        <v>285</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>21</v>
@@ -5164,51 +5014,47 @@
         <v>21</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>21</v>
+        <v>286</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>282</v>
+        <v>21</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>133</v>
+        <v>288</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>21</v>
       </c>
@@ -5256,42 +5102,42 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>131</v>
+        <v>291</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>21</v>
+        <v>292</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>21</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5314,18 +5160,16 @@
         <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>189</v>
+        <v>288</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="N32" s="2"/>
-      <c r="O32" t="s" s="2">
-        <v>289</v>
-      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>21</v>
       </c>
@@ -5349,13 +5193,13 @@
         <v>21</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>183</v>
+        <v>21</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>290</v>
+        <v>21</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>291</v>
+        <v>21</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>21</v>
@@ -5373,7 +5217,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5388,27 +5232,27 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>21</v>
+        <v>297</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AM32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AO32" t="s" s="2">
-        <v>21</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5416,7 +5260,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>88</v>
@@ -5431,13 +5275,13 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>294</v>
+        <v>255</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5488,10 +5332,10 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>88</v>
@@ -5503,27 +5347,27 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>297</v>
+        <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>21</v>
+        <v>303</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>21</v>
+        <v>304</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5534,7 +5378,7 @@
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>21</v>
@@ -5546,13 +5390,13 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5603,13 +5447,13 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
@@ -5621,13 +5465,13 @@
         <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>21</v>
+        <v>310</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>21</v>
@@ -5635,10 +5479,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5661,17 +5505,15 @@
         <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -5720,7 +5562,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5735,27 +5577,27 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>311</v>
+        <v>21</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5766,7 +5608,7 @@
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>21</v>
@@ -5778,15 +5620,17 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>189</v>
+        <v>319</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -5811,13 +5655,13 @@
         <v>21</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>183</v>
+        <v>21</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>315</v>
+        <v>21</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>316</v>
+        <v>21</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>21</v>
@@ -5835,13 +5679,13 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>21</v>
@@ -5853,24 +5697,24 @@
         <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>318</v>
+        <v>21</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>319</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5878,7 +5722,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>88</v>
@@ -5893,13 +5737,13 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>321</v>
+        <v>222</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5950,7 +5794,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5968,24 +5812,24 @@
         <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>326</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6008,13 +5852,13 @@
         <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>321</v>
+        <v>228</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>328</v>
+        <v>229</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>329</v>
+        <v>230</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6065,7 +5909,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>327</v>
+        <v>231</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6077,13 +5921,13 @@
         <v>21</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>330</v>
+        <v>232</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>21</v>
@@ -6092,26 +5936,26 @@
         <v>21</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>331</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>21</v>
@@ -6120,18 +5964,20 @@
         <v>21</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>333</v>
+        <v>134</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>334</v>
+        <v>135</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>21</v>
@@ -6180,74 +6026,78 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>332</v>
+        <v>235</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>336</v>
+        <v>232</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>337</v>
+        <v>21</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>338</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>21</v>
+        <v>237</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>333</v>
+        <v>134</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>340</v>
+        <v>238</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>21</v>
       </c>
@@ -6295,42 +6145,42 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>339</v>
+        <v>240</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>342</v>
+        <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>343</v>
+        <v>131</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>337</v>
+        <v>21</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>338</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6338,7 +6188,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>88</v>
@@ -6353,13 +6203,13 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6410,10 +6260,10 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>88</v>
@@ -6428,24 +6278,24 @@
         <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>348</v>
+        <v>21</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>349</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6456,7 +6306,7 @@
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>21</v>
@@ -6468,13 +6318,13 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>351</v>
+        <v>181</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6501,13 +6351,13 @@
         <v>21</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>21</v>
+        <v>340</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>21</v>
+        <v>341</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>21</v>
@@ -6525,13 +6375,13 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
@@ -6543,24 +6393,24 @@
         <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>354</v>
+        <v>272</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>21</v>
+        <v>343</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6583,13 +6433,13 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>357</v>
+        <v>181</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6616,13 +6466,13 @@
         <v>21</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>21</v>
+        <v>347</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>21</v>
+        <v>348</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>21</v>
@@ -6640,7 +6490,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6655,27 +6505,27 @@
         <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>21</v>
+        <v>350</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>362</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6698,17 +6548,15 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -6757,7 +6605,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6775,13 +6623,13 @@
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>21</v>
+        <v>356</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>21</v>
@@ -6789,21 +6637,21 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>21</v>
+        <v>358</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>21</v>
@@ -6815,15 +6663,17 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>274</v>
+        <v>359</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -6872,13 +6722,13 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>21</v>
@@ -6890,13 +6740,13 @@
         <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>373</v>
+        <v>21</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>21</v>
@@ -6904,10 +6754,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6918,7 +6768,7 @@
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>21</v>
@@ -6930,15 +6780,17 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>217</v>
+        <v>365</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>218</v>
+        <v>366</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -6987,25 +6839,25 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>220</v>
+        <v>364</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>221</v>
+        <v>369</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
@@ -7014,936 +6866,6 @@
         <v>21</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="E47" s="2"/>
-      <c r="F47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K47" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O47" s="2"/>
-      <c r="P47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q47" s="2"/>
-      <c r="R47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="E48" s="2"/>
-      <c r="F48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K48" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="P48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q48" s="2"/>
-      <c r="R48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K49" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
-      <c r="P49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q49" s="2"/>
-      <c r="R49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
-      <c r="P50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
-      <c r="P51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
-      <c r="P52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="O53" s="2"/>
-      <c r="P53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O54" s="2"/>
-      <c r="P54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO54" t="s" s="2">
         <v>21</v>
       </c>
     </row>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationdispense.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationdispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-15T19:11:07+00:00</t>
+    <t>2026-01-16T14:21:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationdispense.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationdispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-16T14:21:16+00:00</t>
+    <t>2026-01-19T10:22:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationdispense.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationdispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T10:22:08+00:00</t>
+    <t>2026-01-20T10:13:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationdispense.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationdispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T10:13:19+00:00</t>
+    <t>2026-01-21T17:03:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationdispense.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationdispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T17:03:29+00:00</t>
+    <t>2026-01-22T09:24:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationdispense.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationdispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T09:24:15+00:00</t>
+    <t>2026-01-22T12:59:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationdispense.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationdispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T12:59:21+00:00</t>
+    <t>2026-01-22T14:02:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationdispense.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationdispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T14:02:02+00:00</t>
+    <t>2026-01-23T19:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationdispense.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medicationdispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-23T19:34:42+00:00</t>
+    <t>2026-01-26T15:48:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
